--- a/artfynd/A 22269-2026 artfynd.xlsx
+++ b/artfynd/A 22269-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99376771</v>
+        <v>100398455</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -731,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576849.3128686916</v>
+        <v>576834</v>
       </c>
       <c r="R2" t="n">
-        <v>6713619.808498494</v>
+        <v>6713559</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,29 +751,29 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
@@ -807,12 +797,7 @@
         <v>100395656</v>
       </c>
       <c r="B3" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -860,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576927.3250787243</v>
+        <v>576928</v>
       </c>
       <c r="R3" t="n">
-        <v>6713682.484349295</v>
+        <v>6713682</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -935,12 +920,7 @@
         <v>100397825</v>
       </c>
       <c r="B4" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,10 +968,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576836.2741903071</v>
+        <v>576836</v>
       </c>
       <c r="R4" t="n">
-        <v>6713630.355802956</v>
+        <v>6713631</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1060,42 +1040,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100396601</v>
+        <v>99376771</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1105,20 +1080,21 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Barkhyttevägen, Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576914.9783960059</v>
+        <v>576849</v>
       </c>
       <c r="R5" t="n">
-        <v>6713660.571341881</v>
+        <v>6713619</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1145,22 +1121,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,18 +1135,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>marianne johansson</t>
+          <t>Maj-Lis Koivisto</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>marianne johansson</t>
+          <t>Maj-Lis Koivisto</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1190,12 +1157,7 @@
         <v>100397489</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576904.8115004103</v>
+        <v>576905</v>
       </c>
       <c r="R6" t="n">
-        <v>6713675.115825868</v>
+        <v>6713675</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1311,6 +1273,128 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100396601</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Barkhyttevägen, Hofors, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>576915</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6713661</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>marianne johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>marianne johansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
